--- a/Ejercicios/Practicas personales/Py-class 04/Transacciones.xlsx
+++ b/Ejercicios/Practicas personales/Py-class 04/Transacciones.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\GitHub\Python_0_to_hero\Ejercicios\Practicas personales\Py-class 04\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julian\Documents\GitHub\Python_0_to_hero\Ejercicios\Practicas personales\Py-class 04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6C9F62-8B83-4ADB-89AF-FD9CFF72CDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF74A11C-692B-43B1-9C70-302044CD9C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transacciones" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="25">
-  <si>
-    <t>#</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="29">
   <si>
     <t>Fecha</t>
   </si>
@@ -37,15 +34,15 @@
     <t>Monto</t>
   </si>
   <si>
+    <t>76628500</t>
+  </si>
+  <si>
+    <t>Retiro</t>
+  </si>
+  <si>
     <t>2025-03-06 11:46</t>
   </si>
   <si>
-    <t>76628500</t>
-  </si>
-  <si>
-    <t>Retiro</t>
-  </si>
-  <si>
     <t>Deposito</t>
   </si>
   <si>
@@ -73,9 +70,18 @@
     <t>2025-03-06 11:54</t>
   </si>
   <si>
+    <t>87387831</t>
+  </si>
+  <si>
+    <t>89613201</t>
+  </si>
+  <si>
     <t>2025-03-06 11:55</t>
   </si>
   <si>
+    <t>24005597</t>
+  </si>
+  <si>
     <t>2025-03-06 11:56</t>
   </si>
   <si>
@@ -95,13 +101,22 @@
   </si>
   <si>
     <t>2025-03-06 11:62</t>
+  </si>
+  <si>
+    <t>2025-03-08 16:24</t>
+  </si>
+  <si>
+    <t>Z</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,12 +128,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -161,7 +170,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -464,633 +473,643 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="15.26953125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B2" s="2">
-        <v>45723.490277777775</v>
+        <v>45723.490277777782</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3">
         <v>190</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
         <v>45724.490277719909</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>370</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5">
         <v>550</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" s="2">
         <v>45725.490277719909</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>730</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7">
         <v>910</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
         <v>45726.490277719909</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E8">
         <v>1090</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9">
         <v>1270</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
         <v>45727.490277719909</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E10">
         <v>1450</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E11">
         <v>1630</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12" s="2">
         <v>45728.490277719909</v>
       </c>
       <c r="C12" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E12">
         <v>1810</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13">
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B14" s="2">
         <v>45729.490277719909</v>
       </c>
       <c r="C14" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E14">
         <v>2170</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15">
         <v>2350</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B16" s="2">
         <v>45728.490277719909</v>
       </c>
-      <c r="C16">
-        <v>76628500</v>
+      <c r="C16" t="s">
+        <v>4</v>
       </c>
       <c r="D16" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E16">
         <v>2530</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17">
-        <v>76628500</v>
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>4</v>
       </c>
       <c r="D17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17">
         <v>600</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="2">
         <v>45729.490277719909</v>
       </c>
-      <c r="C18">
-        <v>76628500</v>
+      <c r="C18" t="s">
+        <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E18">
         <v>2890</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19">
-        <v>76628500</v>
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19">
         <v>3070</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="2">
         <v>45730.490277719909</v>
       </c>
-      <c r="C20">
-        <v>76628500</v>
+      <c r="C20" t="s">
+        <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E20">
         <v>3250</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21">
-        <v>76628500</v>
+        <v>14</v>
+      </c>
+      <c r="C21" t="s">
+        <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21">
         <v>3430</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="2">
         <v>45729.490277719909</v>
       </c>
-      <c r="C22">
-        <v>76628500</v>
+      <c r="C22" t="s">
+        <v>4</v>
       </c>
       <c r="D22" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>3610</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23">
-        <v>76628500</v>
+        <v>13</v>
+      </c>
+      <c r="C23" t="s">
+        <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E23">
         <v>3790</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="2">
         <v>45730.490277719909</v>
       </c>
-      <c r="C24">
-        <v>76628500</v>
+      <c r="C24" t="s">
+        <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E24">
         <v>3970</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25">
-        <v>76628500</v>
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
+        <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25">
         <v>4150</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="2">
         <v>45731.490277719909</v>
       </c>
-      <c r="C26">
-        <v>76628500</v>
+      <c r="C26" t="s">
+        <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E26">
         <v>4330</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" t="s">
         <v>16</v>
       </c>
-      <c r="C27">
-        <v>87387831</v>
-      </c>
       <c r="D27" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27">
         <v>4330</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="2">
         <v>45732.490277719909</v>
       </c>
-      <c r="C28">
-        <v>89613201</v>
+      <c r="C28" t="s">
+        <v>17</v>
       </c>
       <c r="D28" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E28">
         <v>4330</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29">
-        <v>24005597</v>
+        <v>18</v>
+      </c>
+      <c r="C29" t="s">
+        <v>19</v>
       </c>
       <c r="D29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E29">
         <v>4330</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="2">
         <v>45733.490277719909</v>
       </c>
-      <c r="C30">
-        <v>24005597</v>
+      <c r="C30" t="s">
+        <v>19</v>
       </c>
       <c r="D30" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E30">
         <v>4330</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31">
-        <v>24005597</v>
+        <v>20</v>
+      </c>
+      <c r="C31" t="s">
+        <v>19</v>
       </c>
       <c r="D31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E31">
         <v>4330</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32" s="2">
         <v>45734.490277719909</v>
       </c>
-      <c r="C32">
-        <v>24005597</v>
+      <c r="C32" t="s">
+        <v>19</v>
       </c>
       <c r="D32" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E32">
         <v>4330</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" t="s">
         <v>19</v>
       </c>
-      <c r="C33">
-        <v>24005597</v>
-      </c>
       <c r="D33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E33">
         <v>4330</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="2">
         <v>45735.490277719909</v>
       </c>
-      <c r="C34">
-        <v>24005597</v>
+      <c r="C34" t="s">
+        <v>19</v>
       </c>
       <c r="D34" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E34">
         <v>4330</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35">
-        <v>24005597</v>
+        <v>22</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
       </c>
       <c r="D35" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E35">
         <v>4330</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="2">
         <v>45736.490277719909</v>
       </c>
-      <c r="C36">
-        <v>89613201</v>
+      <c r="C36" t="s">
+        <v>17</v>
       </c>
       <c r="D36" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E36">
         <v>4330</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>21</v>
-      </c>
-      <c r="C37">
-        <v>89613201</v>
+        <v>23</v>
+      </c>
+      <c r="C37" t="s">
+        <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E37">
         <v>4330</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="2">
         <v>45737.490277719909</v>
       </c>
-      <c r="C38">
-        <v>89613201</v>
+      <c r="C38" t="s">
+        <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E38">
         <v>4330</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39">
-        <v>89613201</v>
+        <v>24</v>
+      </c>
+      <c r="C39" t="s">
+        <v>17</v>
       </c>
       <c r="D39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E39">
         <v>4330</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" s="2">
         <v>45738.490277719909</v>
       </c>
-      <c r="C40">
-        <v>89613201</v>
+      <c r="C40" t="s">
+        <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E40">
         <v>4330</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>23</v>
-      </c>
-      <c r="C41">
-        <v>89613201</v>
+        <v>25</v>
+      </c>
+      <c r="C41" t="s">
+        <v>17</v>
       </c>
       <c r="D41" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E41">
         <v>4330</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" s="2">
         <v>45739.490277719909</v>
       </c>
-      <c r="C42">
-        <v>89613201</v>
+      <c r="C42" t="s">
+        <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E42">
         <v>4330</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43">
-        <v>89613201</v>
+        <v>26</v>
+      </c>
+      <c r="C43" t="s">
+        <v>17</v>
       </c>
       <c r="D43" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E43">
         <v>4330</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" s="2">
         <v>45740.490277719909</v>
       </c>
-      <c r="C44">
-        <v>89613201</v>
+      <c r="C44" t="s">
+        <v>17</v>
       </c>
       <c r="D44" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E44">
         <v>4330</v>
       </c>
     </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>